--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2518,7 +2518,7 @@
         <v>134028852</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>136230934</v>
       </c>
       <c r="B28" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2413,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124667767</v>
+        <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>96841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,37 +2424,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Iland, Iland, Vrm</t>
+          <t>Iland, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418811</v>
+        <v>418726</v>
       </c>
       <c r="R17" t="n">
-        <v>6587533</v>
+        <v>6587663</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,12 +2478,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,44 +2508,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Poul Torjusen</t>
+          <t>Ludvig Stommendal</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Poul Torjusen</t>
+          <t>Ludvig Stommendal</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124667767</t>
+          <t>https://artportalen.se/Sighting/137367346</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134028852</v>
+        <v>124667767</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2544,27 +2554,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Iland, Iland, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418717</v>
+        <v>418811</v>
       </c>
       <c r="R18" t="n">
-        <v>6587159</v>
+        <v>6587533</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2588,136 +2590,90 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Har svårt att bedöma hur pass färska ringhacken är? Bör kanske snarare betraktas som äldre?</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Poul Torjusen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Poul Torjusen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134028852</t>
+          <t>https://artportalen.se/Sighting/124667767</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114477634</v>
+        <v>134028852</v>
       </c>
       <c r="B19" t="n">
-        <v>4775</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Iland, Vrm</t>
+          <t>Iland, Iland, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418779</v>
+        <v>418717</v>
       </c>
       <c r="R19" t="n">
-        <v>6587370</v>
+        <v>6587159</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,51 +2700,87 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Har svårt att bedöma hur pass färska ringhacken är? Bör kanske snarare betraktas som äldre?</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Karlstads kommun - NVI Steffensminne</t>
-        </is>
-      </c>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477634</t>
+          <t>https://artportalen.se/Sighting/134028852</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114477683</v>
+        <v>114477634</v>
       </c>
       <c r="B20" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,21 +2788,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2834,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418658</v>
+        <v>418779</v>
       </c>
       <c r="R20" t="n">
-        <v>6587107</v>
+        <v>6587370</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,38 +2891,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477683</t>
+          <t>https://artportalen.se/Sighting/114477634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114477637</v>
+        <v>114477683</v>
       </c>
       <c r="B21" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2938,9 +2930,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2949,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418850</v>
+        <v>418658</v>
       </c>
       <c r="R21" t="n">
-        <v>6587440</v>
+        <v>6587107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3014,38 +3011,38 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477637</t>
+          <t>https://artportalen.se/Sighting/114477683</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114477619</v>
+        <v>114477637</v>
       </c>
       <c r="B22" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3053,14 +3050,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3069,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418855</v>
+        <v>418850</v>
       </c>
       <c r="R22" t="n">
-        <v>6587667</v>
+        <v>6587440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3134,13 +3126,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477619</t>
+          <t>https://artportalen.se/Sighting/114477637</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114477622</v>
+        <v>114477619</v>
       </c>
       <c r="B23" t="n">
         <v>5199</v>
@@ -3189,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>418619</v>
+        <v>418855</v>
       </c>
       <c r="R23" t="n">
-        <v>6587120</v>
+        <v>6587667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3254,16 +3246,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477622</t>
+          <t>https://artportalen.se/Sighting/114477619</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114477700</v>
+        <v>114477622</v>
       </c>
       <c r="B24" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,21 +3263,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3309,13 +3301,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418689</v>
+        <v>418619</v>
       </c>
       <c r="R24" t="n">
-        <v>6587205</v>
+        <v>6587120</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3374,16 +3366,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114477700</t>
+          <t>https://artportalen.se/Sighting/114477622</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119440642</v>
+        <v>114477700</v>
       </c>
       <c r="B25" t="n">
-        <v>99038</v>
+        <v>8444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,42 +3383,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223597</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långenäs, Vrm</t>
+          <t>Iland, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>418929</v>
+        <v>418689</v>
       </c>
       <c r="R25" t="n">
-        <v>6587964</v>
+        <v>6587205</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3450,22 +3451,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3485,23 +3476,23 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Åsa Weiss</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
+          <t>Karlstads kommun - NVI Steffensminne</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119440642</t>
+          <t>https://artportalen.se/Sighting/114477700</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119440643</v>
+        <v>119440642</v>
       </c>
       <c r="B26" t="n">
         <v>99038</v>
@@ -3527,7 +3518,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3541,13 +3532,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>418945</v>
+        <v>418929</v>
       </c>
       <c r="R26" t="n">
-        <v>6587767</v>
+        <v>6587964</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3576,7 +3567,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3586,7 +3577,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3616,66 +3607,59 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119440643</t>
+          <t>https://artportalen.se/Sighting/119440642</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>98002133</v>
+        <v>119440643</v>
       </c>
       <c r="B27" t="n">
-        <v>57874</v>
+        <v>99038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100001</v>
+        <v>223597</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stockfallet, Fornåker, Edsgatan, Vrm</t>
+          <t>Långenäs, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>417977</v>
+        <v>418945</v>
       </c>
       <c r="R27" t="n">
-        <v>6586977</v>
+        <v>6587767</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3694,27 +3678,27 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Karlstad</t>
+          <t>Alster</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3729,44 +3713,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Jonasson</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Jonasson, Karl Hammar</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Åsa Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98002133</t>
+          <t>https://artportalen.se/Sighting/119440643</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136230934</v>
+        <v>98002133</v>
       </c>
       <c r="B28" t="n">
-        <v>58005</v>
+        <v>57874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3774,22 +3762,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Finnmyrsgatan 11, Karlstadsområdet, Vrm</t>
+          <t>Stockfallet, Fornåker, Edsgatan, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>418003</v>
+        <v>417977</v>
       </c>
       <c r="R28" t="n">
-        <v>6586998</v>
+        <v>6586977</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3816,22 +3811,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3842,56 +3837,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Roger Jonasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Roger Jonasson, Karl Hammar</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136230934</t>
+          <t>https://artportalen.se/Sighting/98002133</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119669864</v>
+        <v>136230934</v>
       </c>
       <c r="B29" t="n">
-        <v>57947</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,46 +3869,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stockfallet skogen, Fornåker, Edsgatan, Vrm</t>
+          <t>Finnmyrsgatan 11, Karlstadsområdet, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>418018</v>
+        <v>418003</v>
       </c>
       <c r="R29" t="n">
-        <v>6587067</v>
+        <v>6586998</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3962,22 +3928,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3988,31 +3954,56 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mas Karin Gustafsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mas Karin Gustafsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119669864</t>
+          <t>https://artportalen.se/Sighting/136230934</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113904626</v>
+        <v>119669864</v>
       </c>
       <c r="B30" t="n">
-        <v>58636</v>
+        <v>57947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4020,21 +4011,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4042,29 +4033,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bråtetorp, Vrm</t>
+          <t>Stockfallet skogen, Fornåker, Edsgatan, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421892</v>
+        <v>418018</v>
       </c>
       <c r="R30" t="n">
-        <v>6586241</v>
+        <v>6587067</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4083,17 +4069,27 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Östra Fågelvik</t>
+          <t>Karlstad</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4108,53 +4104,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Mas Karin Gustafsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Karlstads kommun - NVI Reningsverk</t>
-        </is>
-      </c>
+          <t>Mas Karin Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113904626</t>
+          <t>https://artportalen.se/Sighting/119669864</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98465932</v>
+        <v>113904626</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>58636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4162,19 +4154,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>kronoparken, Vrm</t>
+          <t>Bråtetorp, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420517</v>
+        <v>421892</v>
       </c>
       <c r="R31" t="n">
-        <v>6586101</v>
+        <v>6586241</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4193,17 +4195,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Karlstad</t>
+          <t>Östra Fågelvik</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4218,69 +4220,73 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
+          <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98465932</t>
+          <t>https://artportalen.se/Sighting/113904626</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>57576259</v>
+        <v>98465932</v>
       </c>
       <c r="B32" t="n">
-        <v>96708</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+          <t>kronoparken, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420557</v>
+        <v>420517</v>
       </c>
       <c r="R32" t="n">
-        <v>6585608</v>
+        <v>6586101</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4304,12 +4310,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4324,79 +4330,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Olof Persson, Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57576259</t>
+          <t>https://artportalen.se/Sighting/98465932</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127911180</v>
+        <v>57576259</v>
       </c>
       <c r="B33" t="n">
-        <v>56845</v>
+        <v>96708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100053</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gustaf Frödings gata, 656 38 Alster, Vrm</t>
+          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420500</v>
+        <v>420557</v>
       </c>
       <c r="R33" t="n">
-        <v>6585654</v>
+        <v>6585608</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4420,22 +4416,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:34</t>
+          <t>2015-05-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>08:34</t>
+          <t>2015-09-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4450,53 +4436,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Olof Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127911180</t>
+          <t>https://artportalen.se/Sighting/57576259</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>57624957</v>
+        <v>127911180</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>56845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100053</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4509,24 +4491,24 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Välsviken, S Gustaf Frödings gata, Vrm</t>
+          <t>Gustaf Frödings gata, 656 38 Alster, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420481</v>
+        <v>420500</v>
       </c>
       <c r="R34" t="n">
-        <v>6585613</v>
+        <v>6585654</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4550,12 +4532,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2015-09-16</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4570,44 +4562,48 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Olof Persson, Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624957</t>
+          <t>https://artportalen.se/Sighting/127911180</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>57624961</v>
+        <v>57624957</v>
       </c>
       <c r="B35" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4627,7 +4623,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420517</v>
+        <v>420481</v>
       </c>
       <c r="R35" t="n">
-        <v>6585695</v>
+        <v>6585613</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4697,13 +4693,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624961</t>
+          <t>https://artportalen.se/Sighting/57624957</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>57624963</v>
+        <v>57624961</v>
       </c>
       <c r="B36" t="n">
         <v>58327</v>
@@ -4743,7 +4739,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4752,10 +4748,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420613</v>
+        <v>420517</v>
       </c>
       <c r="R36" t="n">
-        <v>6585732</v>
+        <v>6585695</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4813,38 +4809,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624963</t>
+          <t>https://artportalen.se/Sighting/57624961</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>57624956</v>
+        <v>57624963</v>
       </c>
       <c r="B37" t="n">
-        <v>58676</v>
+        <v>58327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4859,7 +4855,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4868,10 +4864,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420663</v>
+        <v>420613</v>
       </c>
       <c r="R37" t="n">
-        <v>6585631</v>
+        <v>6585732</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4929,60 +4925,65 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57624956</t>
+          <t>https://artportalen.se/Sighting/57624963</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>57584703</v>
+        <v>57624956</v>
       </c>
       <c r="B38" t="n">
-        <v>40300</v>
+        <v>58676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>103055</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+          <t>Välsviken, S Gustaf Frödings gata, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420565</v>
+        <v>420663</v>
       </c>
       <c r="R38" t="n">
-        <v>6585581</v>
+        <v>6585631</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5034,11 +5035,122 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Olof Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624956</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>57584703</v>
+      </c>
+      <c r="B39" t="n">
+        <v>40300</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Välsviken NE, S Gustaf Frödings gata, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>420565</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6585581</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2015-05-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2015-09-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olof Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/57584703</t>
         </is>
@@ -5083,6 +5195,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 2893-2022 artfynd.xlsx
+++ b/artfynd/S 2893-2022 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>137367346</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
